--- a/DateBase/orders/Nhat 48_2026-9-29.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -518,10 +518,138 @@
       <c r="A10" t="str">
         <v>5</v>
       </c>
+      <c r="C10" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F10" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F11" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>75_爱心_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>6</v>
+      </c>
+      <c r="C14" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>75_爱心_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>7</v>
+      </c>
+      <c r="C17" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>8</v>
+      </c>
+      <c r="C18" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>9</v>
+      </c>
+      <c r="C19" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>10</v>
+      </c>
+      <c r="C20" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F20" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>863_干花文竹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>11</v>
+      </c>
+      <c r="C23" t="str">
+        <v>569_灯笼果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -576,7 +704,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>040205039162918150</v>
+        <v>040205039162918151732121116075200200200100155020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-29.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -647,9 +647,44 @@
         <v>20</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>12</v>
+      </c>
+      <c r="C24" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F24" t="str">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>75_爱心_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -704,7 +739,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>040205039162918151732121116075200200200100155020</v>
+        <v>0402050391629181517321211160752002002001001550205740226</v>
       </c>
     </row>
   </sheetData>
